--- a/result.xlsx
+++ b/result.xlsx
@@ -3494,13 +3494,13 @@
         <v>55.33</v>
       </c>
       <c r="K16" t="n">
-        <v>10.89</v>
+        <v>11.14</v>
       </c>
       <c r="L16" t="n">
         <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
         <v>31.79</v>
@@ -3944,13 +3944,13 @@
         <v>151</v>
       </c>
       <c r="K20" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="L20" t="n">
         <v>1.04</v>
       </c>
       <c r="M20" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="N20" t="n">
         <v>4.32</v>
@@ -5849,13 +5849,13 @@
         <v>55.33</v>
       </c>
       <c r="K16" t="n">
-        <v>10.89</v>
+        <v>11.14</v>
       </c>
       <c r="L16" t="n">
         <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
         <v>31.79</v>
@@ -6299,13 +6299,13 @@
         <v>151</v>
       </c>
       <c r="K20" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="L20" t="n">
         <v>1.04</v>
       </c>
       <c r="M20" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="N20" t="n">
         <v>4.32</v>
@@ -6415,7 +6415,7 @@
         <v>3.98</v>
       </c>
       <c r="M21" t="n">
-        <v>64.29000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="N21" t="n">
         <v>9.27</v>
@@ -9079,13 +9079,13 @@
         <v>26.5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="L45" t="n">
         <v>2.42</v>
       </c>
       <c r="M45" t="n">
-        <v>36.09</v>
+        <v>35.36</v>
       </c>
       <c r="N45" t="n">
         <v>7.71</v>
@@ -9621,13 +9621,13 @@
         <v>174</v>
       </c>
       <c r="K50" t="n">
-        <v>19.88</v>
+        <v>20.33</v>
       </c>
       <c r="L50" t="n">
         <v>3.77</v>
       </c>
       <c r="M50" t="n">
-        <v>74.86</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>12.1</v>
@@ -10489,13 +10489,13 @@
         <v>165</v>
       </c>
       <c r="K58" t="n">
-        <v>22.42</v>
+        <v>17.18</v>
       </c>
       <c r="L58" t="n">
         <v>2.09</v>
       </c>
       <c r="M58" t="n">
-        <v>46.93</v>
+        <v>35.96</v>
       </c>
       <c r="N58" t="n">
         <v>12.25</v>
@@ -11030,16 +11030,16 @@
         <v>3.33</v>
       </c>
       <c r="J63" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K63" t="n">
         <v>14.49</v>
       </c>
       <c r="L63" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="M63" t="n">
-        <v>17.65</v>
+        <v>16.93</v>
       </c>
       <c r="N63" t="n">
         <v>6.8</v>
@@ -13266,13 +13266,13 @@
         <v>55.33</v>
       </c>
       <c r="K16" t="n">
-        <v>10.89</v>
+        <v>11.14</v>
       </c>
       <c r="L16" t="n">
         <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
         <v>31.79</v>
@@ -13716,13 +13716,13 @@
         <v>151</v>
       </c>
       <c r="K20" t="n">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="L20" t="n">
         <v>1.04</v>
       </c>
       <c r="M20" t="n">
-        <v>13.18</v>
+        <v>13.19</v>
       </c>
       <c r="N20" t="n">
         <v>4.32</v>
@@ -13832,7 +13832,7 @@
         <v>3.98</v>
       </c>
       <c r="M21" t="n">
-        <v>64.29000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="N21" t="n">
         <v>9.27</v>
@@ -16496,13 +16496,13 @@
         <v>26.5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="L45" t="n">
         <v>2.42</v>
       </c>
       <c r="M45" t="n">
-        <v>36.09</v>
+        <v>35.36</v>
       </c>
       <c r="N45" t="n">
         <v>7.71</v>
@@ -17038,13 +17038,13 @@
         <v>174</v>
       </c>
       <c r="K50" t="n">
-        <v>19.88</v>
+        <v>20.33</v>
       </c>
       <c r="L50" t="n">
         <v>3.77</v>
       </c>
       <c r="M50" t="n">
-        <v>74.86</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="N50" t="n">
         <v>12.1</v>
@@ -17906,13 +17906,13 @@
         <v>165</v>
       </c>
       <c r="K58" t="n">
-        <v>22.42</v>
+        <v>17.18</v>
       </c>
       <c r="L58" t="n">
         <v>2.09</v>
       </c>
       <c r="M58" t="n">
-        <v>46.93</v>
+        <v>35.96</v>
       </c>
       <c r="N58" t="n">
         <v>12.25</v>
@@ -18447,16 +18447,16 @@
         <v>3.33</v>
       </c>
       <c r="J63" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K63" t="n">
         <v>14.49</v>
       </c>
       <c r="L63" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="M63" t="n">
-        <v>17.65</v>
+        <v>16.93</v>
       </c>
       <c r="N63" t="n">
         <v>6.8</v>
